--- a/excel/solar_answer_key.xlsx
+++ b/excel/solar_answer_key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahadam/Documents/Projects/Solar Project Finance/solar-project-finance/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899B3DA6-5A51-8C4B-B4FA-D2F6CD88BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A93E56A-5B61-2048-9F2C-3E28051F7B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/excel/solar_answer_key.xlsx
+++ b/excel/solar_answer_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahadam/Documents/Projects/Solar Project Finance/solar-project-finance/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A93E56A-5B61-2048-9F2C-3E28051F7B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC18BA45-D4DC-ED44-8B9E-5B40C4FB50C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="17060" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1330,7 +1330,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1407,8 +1407,6 @@
     <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -6335,7 +6333,7 @@
       <c r="B9" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C9" s="70">
+      <c r="C9" s="37">
         <f>+SUM(E9:AW9)</f>
         <v>9662400</v>
       </c>
@@ -6964,7 +6962,7 @@
       <c r="B13" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="70">
+      <c r="C13" s="37">
         <f>+PMT(Inputs!$F$25, Inputs!$F$24, -SUM(Debt!$E$12:$AW$12))</f>
         <v>31015308.143440913</v>
       </c>
@@ -10672,7 +10670,7 @@
         <f>+SUM(E10:AW10)</f>
         <v>-177355892.97576028</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="70" t="s">
         <v>337</v>
       </c>
       <c r="E10" s="36">
@@ -10867,7 +10865,7 @@
         <f>+SUM(E11:AW11)</f>
         <v>243662750.24874568</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="70" t="s">
         <v>338</v>
       </c>
       <c r="E11" s="36">
@@ -12286,7 +12284,7 @@
         <v>0.06</v>
       </c>
       <c r="C39" s="66">
-        <f>+Inputs!$H$34</f>
+        <f>+Inputs!$D$34+Inputs!$D$40/10000</f>
         <v>0.09</v>
       </c>
       <c r="D39" s="60">
@@ -12592,18 +12590,18 @@
         <v>0.06</v>
       </c>
       <c r="C49" s="66">
-        <f>+Inputs!$H$34</f>
-        <v>0.09</v>
+        <f>+Inputs!$E$34+Inputs!$E$40/10000</f>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="D49" s="60">
         <v>1.8761722323491292</v>
       </c>
       <c r="E49" s="60">
-        <v>2.3820456847399569</v>
+        <v>2.3465600000000002</v>
       </c>
       <c r="F49" s="41">
         <f t="shared" ref="F49:F55" si="2">+ABS(E49-D49)</f>
-        <v>0.5058734523908277</v>
+        <v>0.47038776765087098</v>
       </c>
       <c r="G49" s="61">
         <v>-6.2835797002924687E-2</v>
@@ -12920,7 +12918,7 @@
       <c r="A11" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B11" s="71" cm="1">
+      <c r="B11" s="69" cm="1">
         <f t="array" ref="B11">+IF(SUMPRODUCT(ABS(Operations!E10:AW10),1-Timeline!E8:AW8)&gt;0,1,0)</f>
         <v>0</v>
       </c>
@@ -12930,7 +12928,7 @@
       <c r="A12" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B12" s="71" cm="1">
+      <c r="B12" s="69" cm="1">
         <f t="array" ref="B12">+IF(SUMPRODUCT(--ISNUMBER(CashFlow!E8:AW8),1-Timeline!E10:AW10)&gt;0,1,0)</f>
         <v>0</v>
       </c>
